--- a/Documents/Deliverables_LB/BOM/LED Board (LB)_Altium.xlsx
+++ b/Documents/Deliverables_LB/BOM/LED Board (LB)_Altium.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\FranciscoGimenez-HCDSHardware\Documents\Deliverables_LB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\FranciscoGimenez-HCDSHardware\Documents\Deliverables_LB\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70E9F7AC-7395-49DF-A1E6-4CDBF18B5F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BC6090F-7228-4056-A69B-24C1E4CB4CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6255" yWindow="735" windowWidth="10335" windowHeight="7830" xr2:uid="{3779C1B0-F250-4A7D-ADD8-79E256EB99CE}"/>
+    <workbookView xWindow="2460" yWindow="2460" windowWidth="10335" windowHeight="7830" xr2:uid="{A60C8DF0-72F9-43A9-998C-314CAE0D21F4}"/>
   </bookViews>
   <sheets>
     <sheet name="LED Board (LB)_Altium" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,7 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>Comment</t>
   </si>
@@ -58,37 +59,43 @@
     <t>Manufacturer</t>
   </si>
   <si>
-    <t>RED LED</t>
-  </si>
-  <si>
-    <t>KTRLIGHT 0201 SMD LED Red 620-625nm 0.06W high bright quality 0201 Led chip led lamp beads surface mounted SMD LED datasheet</t>
-  </si>
-  <si>
-    <t>LED1, LED2, LED3, LED4, LED5, LED6, LED7, LED8, LED9, LED10, LED11, LED12, LED13, LED14, LED15, LED16, LED17, LED18, LED19, LED20, LED21, LED22, LED23, LED24, LED25, LED26, LED27, LED28, LED29, LED30, LED31, LED32, LED33, LED34, LED35, LED36, LED37, LED38, LED39, LED40, LED41, LED42, LED43, LED44, LED45, LED46, LED47, LED48, LED49, LED50, LED51, LED52, LED53, LED54, LED55, LED56, LED57, LED58, LED59, LED60, LED61, LED62, LED63, LED64, LED65, LED66, LED67, LED68, LED69, LED70, LED71, LED72</t>
-  </si>
-  <si>
-    <t>LED 0201</t>
-  </si>
-  <si>
-    <t>KTRLIGHT</t>
-  </si>
-  <si>
-    <t>200R</t>
-  </si>
-  <si>
-    <t>RES 200 OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>R1, R2, R3, R4, R5, R6, R7, R8, R9, R10, R11, R12, R13, R14, R15, R16, R17, R18, R19, R20, R21, R22, R23, R24, R25, R26, R27, R28, R29, R30, R31, R32, R33, R34, R35, R36</t>
-  </si>
-  <si>
-    <t>Res0402</t>
-  </si>
-  <si>
-    <t>RC0402FR-07200RL</t>
+    <t>0.1uF</t>
+  </si>
+  <si>
+    <t>Cap Ceramic 0.1uF 10V X5R 10% SMD 0201 85C Paper T/R</t>
+  </si>
+  <si>
+    <t>C1, C2, C3, C4, C5, C6, C7, C8, C9, C10, C11, C12, C13, C14</t>
+  </si>
+  <si>
+    <t>CAP 0201</t>
+  </si>
+  <si>
+    <t>CC0201KRX5R6BB104</t>
   </si>
   <si>
     <t>Yageo</t>
+  </si>
+  <si>
+    <t>HDR_F_1X3</t>
+  </si>
+  <si>
+    <t>3 POS 2.54mm female header</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>WS2812B-Mini</t>
+  </si>
+  <si>
+    <t>SMD,3.5x3.5mm Light Emitting Diodes (LED) RoHS</t>
+  </si>
+  <si>
+    <t>LED0, LED1, LED2, LED3, LED4, LED5, LED6, LED7, LED8, LED9, LED10, LED11, LED12, LED13</t>
+  </si>
+  <si>
+    <t>Worldsemi</t>
   </si>
 </sst>
 </file>
@@ -147,16 +154,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,89 +471,106 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3009500D-F085-4DA0-99B5-A5EC6867920B}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDE59038-60E7-4ACB-8F6E-4CD8CC653E28}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="19.7109375" customWidth="1"/>
     <col min="7" max="7" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="360" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="4">
-        <v>72</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="F2" s="1">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" ht="135" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="4">
-        <v>36</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1">
+        <v>14</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.30555555555555558" bottom="0.30555555555555558" header="0" footer="0"/>
-  <pageSetup scale="98" orientation="landscape" blackAndWhite="1" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>